--- a/outputs/tables/Manuscript_Results_Tables.xlsx
+++ b/outputs/tables/Manuscript_Results_Tables.xlsx
@@ -1142,13 +1142,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.547</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>0.546</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>0.419</v>
+        <v>0.443</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>-0.003</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.015</v>
+        <v>-0.014</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1184,13 +1184,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.17</v>
+        <v>0.177</v>
       </c>
       <c r="C4" t="n">
-        <v>0.156</v>
+        <v>0.164</v>
       </c>
       <c r="D4" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.079</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1205,13 +1205,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.179</v>
+        <v>0.167</v>
       </c>
       <c r="C5" t="n">
-        <v>0.172</v>
+        <v>0.16</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.073</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1226,13 +1226,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.394</v>
+        <v>0.388</v>
       </c>
       <c r="C6" t="n">
-        <v>0.391</v>
+        <v>0.385</v>
       </c>
       <c r="D6" t="n">
-        <v>0.268</v>
+        <v>0.261</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1318,35 +1318,35 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.07650779685218929</v>
+        <v>0.0760077714839279</v>
       </c>
       <c r="C2" t="n">
-        <v>0.07895963329386189</v>
+        <v>0.0780674544757365</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0308035977842758</v>
+        <v>0.0306551759222176</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0239943123444116</v>
+        <v>0.0236087058210359</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1445398715060241</v>
+        <v>0.1419704131728399</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0024</v>
+        <v>0.003</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1364522444178099</v>
+        <v>0.0855127484000439</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0484</v>
+        <v>0.2182</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Complementary (partial)</t>
+          <t>Indirect-only mediation (full)</t>
         </is>
       </c>
     </row>
@@ -1357,28 +1357,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.0787684574925126</v>
+        <v>-0.0918005937067993</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.0803679536952024</v>
+        <v>-0.0929295902307684</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0275321946396439</v>
+        <v>0.0296936868258892</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1377091627879118</v>
+        <v>-0.1550931078669193</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0308624042473663</v>
+        <v>-0.0392713359831372</v>
       </c>
       <c r="G3" t="n">
         <v>0.0005999999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0507954206202218</v>
+        <v>-0.0476699106963272</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3884</v>
+        <v>0.4148</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
@@ -1396,27 +1396,27 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0819338587545832</v>
+        <v>0.0498108203755562</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0817715645269792</v>
+        <v>0.0500978120699272</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0425914881938685</v>
+        <v>0.0407940005742073</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0004628244323536</v>
+        <v>-0.0273094679696942</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1668919107142145</v>
+        <v>0.132291327272095</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0484</v>
+        <v>0.2182</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1431,28 +1431,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.0305005229942094</v>
+        <v>-0.0277675247660773</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.0303357673939008</v>
+        <v>-0.0276163230228993</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0353056634312206</v>
+        <v>0.034181178481901</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.098507141045568</v>
+        <v>-0.092662973381548</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0403022840135776</v>
+        <v>0.0406744150814752</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3884</v>
+        <v>0.4148</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1145290810024277</v>
+        <v>-0.1468015323307813</v>
       </c>
       <c r="I5" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0014</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -1470,22 +1470,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0459397282005677</v>
+        <v>0.0442742108442197</v>
       </c>
       <c r="C6" t="n">
-        <v>0.047806097265603</v>
+        <v>0.0457972923449941</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0197380416115361</v>
+        <v>0.0190263543003398</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0140972934766916</v>
+        <v>0.0133995115424782</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0904005825617898</v>
+        <v>0.0869960542872598</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0024</v>
+        <v>0.003</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -1505,28 +1505,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.0472971602485826</v>
+        <v>-0.0534734641214788</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.0485779096150465</v>
+        <v>-0.0544942498465238</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0176470229205687</v>
+        <v>0.0187108337413342</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0868763911894502</v>
+        <v>-0.0951208510862783</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0175769236618094</v>
+        <v>-0.0217983927585407</v>
       </c>
       <c r="G7" t="n">
         <v>0.0005999999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1145290810024277</v>
+        <v>-0.1468015323307813</v>
       </c>
       <c r="I7" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0014</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
@@ -1610,10 +1610,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="D2" t="n">
-        <v>25.3181</v>
+        <v>27.0399</v>
       </c>
       <c r="E2" t="n">
         <v>5</v>
@@ -1622,7 +1622,7 @@
         <v>0.0001</v>
       </c>
       <c r="G2" t="n">
-        <v>27.5157</v>
+        <v>32.349</v>
       </c>
       <c r="H2" t="n">
         <v>2</v>
@@ -1643,25 +1643,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="D3" t="n">
-        <v>9.860200000000001</v>
+        <v>11.3732</v>
       </c>
       <c r="E3" t="n">
         <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0793</v>
+        <v>0.0445</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7628</v>
+        <v>2.2451</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4142</v>
+        <v>0.3254</v>
       </c>
     </row>
     <row r="4">
@@ -1676,25 +1676,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="D4" t="n">
-        <v>18.9594</v>
+        <v>19.3283</v>
       </c>
       <c r="E4" t="n">
         <v>5</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002</v>
+        <v>0.0017</v>
       </c>
       <c r="G4" t="n">
-        <v>16.9944</v>
+        <v>16.0177</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0002</v>
+        <v>0.0003</v>
       </c>
     </row>
     <row r="5">
@@ -1709,25 +1709,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="D5" t="n">
-        <v>9.457000000000001</v>
+        <v>9.1982</v>
       </c>
       <c r="E5" t="n">
         <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0922</v>
+        <v>0.1014</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0977</v>
+        <v>1.9137</v>
       </c>
       <c r="H5" t="n">
         <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3503</v>
+        <v>0.3841</v>
       </c>
     </row>
   </sheetData>
@@ -1808,28 +1808,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0755</v>
+        <v>-0.0917</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0528</v>
+        <v>0.0517</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1928</v>
+        <v>-0.2067</v>
       </c>
       <c r="G2" t="n">
-        <v>0.013</v>
+        <v>-0.0048</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1116</v>
+        <v>0.0472</v>
       </c>
       <c r="I2" t="n">
-        <v>0.154</v>
+        <v>0.0769</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0123</v>
+        <v>0.0179</v>
       </c>
     </row>
     <row r="3">
@@ -1844,28 +1844,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0515</v>
+        <v>-0.0718</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0245</v>
+        <v>0.025</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1024</v>
+        <v>-0.1263</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001</v>
+        <v>-0.0175</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0496</v>
+        <v>0.0176</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0366</v>
+        <v>0.0044</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0071</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="4">
@@ -1880,28 +1880,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0931</v>
+        <v>-0.0024</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1203</v>
+        <v>0.1198</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3178</v>
+        <v>-0.2329</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1377</v>
+        <v>0.2302</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4152</v>
+        <v>0.978</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4395</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0033</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1916,28 +1916,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0688</v>
+        <v>-0.0381</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0788</v>
+        <v>0.076</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2191</v>
+        <v>-0.1825</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0878</v>
+        <v>0.1106</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3944</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3833</v>
+        <v>0.6162</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0025</v>
+        <v>0.0008</v>
       </c>
     </row>
   </sheetData>
@@ -2028,40 +2028,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="C2" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0515</v>
+        <v>-0.0718</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.0755</v>
+        <v>-0.0917</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1024</v>
+        <v>-0.1263</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.1928</v>
+        <v>-0.2067</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001</v>
+        <v>-0.0175</v>
       </c>
       <c r="I2" t="n">
-        <v>0.013</v>
+        <v>-0.0048</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0496</v>
+        <v>0.0176</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1116</v>
+        <v>0.0472</v>
       </c>
       <c r="L2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -2071,34 +2071,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="C3" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0688</v>
+        <v>-0.0381</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0931</v>
+        <v>-0.0024</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2191</v>
+        <v>-0.1825</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.3178</v>
+        <v>-0.2329</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0878</v>
+        <v>0.1106</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1377</v>
+        <v>0.2302</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3944</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4152</v>
+        <v>0.978</v>
       </c>
       <c r="L3" t="b">
         <v>0</v>
@@ -2170,19 +2170,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.104</v>
+        <v>-0.1103</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2422</v>
+        <v>-0.2512</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0837</v>
+        <v>0.065</v>
       </c>
       <c r="G2" t="n">
-        <v>0.218</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="3">
@@ -2197,19 +2197,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1884</v>
+        <v>-0.2128</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2972</v>
+        <v>-0.3224</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0741</v>
+        <v>-0.0973</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0012</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2224,19 +2224,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2728</v>
+        <v>-0.3154</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4263</v>
+        <v>-0.4719</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1004</v>
+        <v>-0.1582</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0008</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2251,19 +2251,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1287</v>
+        <v>-0.1195</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2244</v>
+        <v>-0.2091</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0396</v>
+        <v>-0.0303</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0076</v>
+        <v>0.0124</v>
       </c>
     </row>
     <row r="6">
@@ -2278,16 +2278,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1863</v>
+        <v>-0.1997</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2628</v>
+        <v>-0.2786</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1117</v>
+        <v>-0.1269</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -2305,16 +2305,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2438</v>
+        <v>-0.28</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3455</v>
+        <v>-0.3887</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1462</v>
+        <v>-0.1831</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -2331,7 +2331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>13.7</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="3">
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="4">
@@ -2387,7 +2387,7 @@
         <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="5">
@@ -2400,7 +2400,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="6">
@@ -2410,36 +2410,36 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>5.9</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cần Thơ</t>
+          <t>Cà Mau</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cà Mau</t>
+          <t>Cần Thơ</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="9">
@@ -2452,7 +2452,7 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="10">
@@ -2465,7 +2465,7 @@
         <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="11">
@@ -2478,7 +2478,7 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="12">
@@ -2491,33 +2491,33 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Bạc Liêu</t>
+          <t>(missing free text)</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>(missing free text)</t>
+          <t>Bạc Liêu</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="15">
@@ -2530,33 +2530,33 @@
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Prefer not to say</t>
+          <t>Biên Hòa</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Biên Hòa</t>
+          <t>Prefer not to say</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="18">
@@ -2569,7 +2569,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="19">
@@ -2582,7 +2582,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="20">
@@ -2595,7 +2595,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="21">
@@ -2608,7 +2608,7 @@
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="22">
@@ -2621,7 +2621,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="23">
@@ -2634,33 +2634,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Wollongong</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>L.A</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
   </sheetData>
@@ -3007,22 +2981,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.83</v>
+        <v>0.831</v>
       </c>
       <c r="D2" t="n">
-        <v>0.91</v>
+        <v>0.913</v>
       </c>
       <c r="E2" t="n">
-        <v>0.911</v>
+        <v>0.914</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>0.736</v>
+        <v>0.742</v>
       </c>
       <c r="H2" t="n">
-        <v>2.207</v>
+        <v>2.237</v>
       </c>
     </row>
     <row r="3">
@@ -3033,14 +3007,14 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.893</v>
+        <v>0.895</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>3.089</v>
+        <v>3.145</v>
       </c>
     </row>
     <row r="4">
@@ -3051,14 +3025,14 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.86</v>
+        <v>0.858</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>2.518</v>
+        <v>2.523</v>
       </c>
     </row>
     <row r="5">
@@ -3069,14 +3043,14 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.845</v>
+        <v>0.854</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>2.317</v>
+        <v>2.419</v>
       </c>
     </row>
     <row r="6">
@@ -3087,14 +3061,14 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.86</v>
+        <v>0.867</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>2.591</v>
+        <v>2.689</v>
       </c>
     </row>
     <row r="7">
@@ -3109,22 +3083,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.867</v>
+        <v>0.878</v>
       </c>
       <c r="D7" t="n">
-        <v>0.907</v>
+        <v>0.915</v>
       </c>
       <c r="E7" t="n">
-        <v>0.909</v>
+        <v>0.916</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>0.783</v>
+        <v>0.797</v>
       </c>
       <c r="H7" t="n">
-        <v>2.451</v>
+        <v>2.628</v>
       </c>
     </row>
     <row r="8">
@@ -3135,14 +3109,14 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.91</v>
+        <v>0.914</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>3.264</v>
+        <v>3.444</v>
       </c>
     </row>
     <row r="9">
@@ -3153,14 +3127,14 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.882</v>
+        <v>0.892</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>2.612</v>
+        <v>2.839</v>
       </c>
     </row>
     <row r="10">
@@ -3171,14 +3145,14 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.88</v>
+        <v>0.888</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>2.694</v>
+        <v>2.836</v>
       </c>
     </row>
     <row r="11">
@@ -3193,22 +3167,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.87</v>
+        <v>0.878</v>
       </c>
       <c r="D11" t="n">
-        <v>0.904</v>
+        <v>0.907</v>
       </c>
       <c r="E11" t="n">
-        <v>0.904</v>
+        <v>0.908</v>
       </c>
       <c r="F11" t="n">
-        <v>0.929</v>
+        <v>0.931</v>
       </c>
       <c r="G11" t="n">
-        <v>0.723</v>
+        <v>0.73</v>
       </c>
       <c r="H11" t="n">
-        <v>2.938</v>
+        <v>3.022</v>
       </c>
     </row>
     <row r="12">
@@ -3219,14 +3193,14 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.867</v>
+        <v>0.871</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>3.121</v>
+        <v>3.136</v>
       </c>
     </row>
     <row r="13">
@@ -3237,14 +3211,14 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.877</v>
+        <v>0.875</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>2.801</v>
+        <v>2.783</v>
       </c>
     </row>
     <row r="14">
@@ -3255,14 +3229,14 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.794</v>
+        <v>0.8</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>1.903</v>
+        <v>1.972</v>
       </c>
     </row>
     <row r="15">
@@ -3273,14 +3247,14 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.841</v>
+        <v>0.844</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>2.253</v>
+        <v>2.312</v>
       </c>
     </row>
     <row r="16">
@@ -3295,22 +3269,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.824</v>
+        <v>0.831</v>
       </c>
       <c r="D16" t="n">
-        <v>0.911</v>
+        <v>0.915</v>
       </c>
       <c r="E16" t="n">
-        <v>0.923</v>
+        <v>0.926</v>
       </c>
       <c r="F16" t="n">
-        <v>0.931</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.701</v>
       </c>
       <c r="H16" t="n">
-        <v>2.115</v>
+        <v>2.204</v>
       </c>
     </row>
     <row r="17">
@@ -3328,7 +3302,7 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>2.347</v>
+        <v>2.391</v>
       </c>
     </row>
     <row r="18">
@@ -3339,14 +3313,14 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.746</v>
+        <v>0.755</v>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>1.935</v>
+        <v>2.007</v>
       </c>
     </row>
     <row r="19">
@@ -3357,14 +3331,14 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.863</v>
+        <v>0.87</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>2.974</v>
+        <v>3.074</v>
       </c>
     </row>
     <row r="20">
@@ -3375,14 +3349,14 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.861</v>
+        <v>0.866</v>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>2.759</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="21">
@@ -3393,14 +3367,14 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.868</v>
+        <v>0.87</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>2.869</v>
+        <v>2.889</v>
       </c>
     </row>
     <row r="22">
@@ -3415,22 +3389,22 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.748</v>
+        <v>0.746</v>
       </c>
       <c r="D22" t="n">
-        <v>0.864</v>
+        <v>0.865</v>
       </c>
       <c r="E22" t="n">
-        <v>0.869</v>
+        <v>0.87</v>
       </c>
       <c r="F22" t="n">
         <v>0.898</v>
       </c>
       <c r="G22" t="n">
-        <v>0.595</v>
+        <v>0.596</v>
       </c>
       <c r="H22" t="n">
-        <v>1.625</v>
+        <v>1.628</v>
       </c>
     </row>
     <row r="23">
@@ -3441,14 +3415,14 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.756</v>
+        <v>0.761</v>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>1.783</v>
+        <v>1.806</v>
       </c>
     </row>
     <row r="24">
@@ -3459,14 +3433,14 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.779</v>
+        <v>0.788</v>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>1.869</v>
+        <v>1.924</v>
       </c>
     </row>
     <row r="25">
@@ -3477,14 +3451,14 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.75</v>
+        <v>0.754</v>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>2.336</v>
+        <v>2.344</v>
       </c>
     </row>
     <row r="26">
@@ -3495,14 +3469,14 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.75</v>
+        <v>0.744</v>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>2.266</v>
+        <v>2.217</v>
       </c>
     </row>
     <row r="27">
@@ -3513,14 +3487,14 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.84</v>
+        <v>0.834</v>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>2.308</v>
+        <v>2.279</v>
       </c>
     </row>
     <row r="28">
@@ -3535,13 +3509,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.819</v>
+        <v>0.829</v>
       </c>
       <c r="D28" t="n">
-        <v>0.867</v>
+        <v>0.866</v>
       </c>
       <c r="E28" t="n">
-        <v>0.873</v>
+        <v>0.872</v>
       </c>
       <c r="F28" t="n">
         <v>0.909</v>
@@ -3550,7 +3524,7 @@
         <v>0.714</v>
       </c>
       <c r="H28" t="n">
-        <v>1.962</v>
+        <v>2.022</v>
       </c>
     </row>
     <row r="29">
@@ -3561,14 +3535,14 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.857</v>
+        <v>0.844</v>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>2.253</v>
+        <v>2.157</v>
       </c>
     </row>
     <row r="30">
@@ -3579,14 +3553,14 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.872</v>
+        <v>0.871</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>2.269</v>
+        <v>2.255</v>
       </c>
     </row>
     <row r="31">
@@ -3597,14 +3571,14 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.83</v>
+        <v>0.834</v>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>1.958</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -3619,13 +3593,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.828</v>
+        <v>0.835</v>
       </c>
       <c r="D32" t="n">
         <v>0.871</v>
       </c>
       <c r="E32" t="n">
-        <v>0.91</v>
+        <v>0.908</v>
       </c>
       <c r="F32" t="n">
         <v>0.909</v>
@@ -3634,7 +3608,7 @@
         <v>0.715</v>
       </c>
       <c r="H32" t="n">
-        <v>1.796</v>
+        <v>1.815</v>
       </c>
     </row>
     <row r="33">
@@ -3645,14 +3619,14 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.82</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>2.148</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="34">
@@ -3663,14 +3637,14 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.837</v>
+        <v>0.835</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>2.51</v>
+        <v>2.529</v>
       </c>
     </row>
     <row r="35">
@@ -3681,14 +3655,14 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.895</v>
+        <v>0.894</v>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>2.346</v>
+        <v>2.365</v>
       </c>
     </row>
   </sheetData>
@@ -3749,7 +3723,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.858</v>
+        <v>0.861</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -3765,10 +3739,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.74</v>
+        <v>0.753</v>
       </c>
       <c r="C3" t="n">
-        <v>0.885</v>
+        <v>0.893</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -3783,13 +3757,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.034</v>
+        <v>0.017</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.063</v>
+        <v>-0.074</v>
       </c>
       <c r="D4" t="n">
-        <v>0.85</v>
+        <v>0.854</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
@@ -3803,16 +3777,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.159</v>
+        <v>0.149</v>
       </c>
       <c r="C5" t="n">
-        <v>0.279</v>
+        <v>0.264</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.261</v>
+        <v>-0.292</v>
       </c>
       <c r="E5" t="n">
-        <v>0.832</v>
+        <v>0.837</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
@@ -3825,19 +3799,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.165</v>
+        <v>0.135</v>
       </c>
       <c r="C6" t="n">
-        <v>0.237</v>
+        <v>0.184</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.15</v>
+        <v>-0.159</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4</v>
+        <v>0.397</v>
       </c>
       <c r="F6" t="n">
-        <v>0.771</v>
+        <v>0.772</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -3849,19 +3823,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.074</v>
+        <v>0.082</v>
       </c>
       <c r="C7" t="n">
-        <v>0.203</v>
+        <v>0.192</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.099</v>
       </c>
       <c r="E7" t="n">
-        <v>0.193</v>
+        <v>0.186</v>
       </c>
       <c r="F7" t="n">
-        <v>0.228</v>
+        <v>0.239</v>
       </c>
       <c r="G7" t="n">
         <v>0.846</v>
@@ -3875,22 +3849,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.285</v>
+        <v>0.287</v>
       </c>
       <c r="C8" t="n">
-        <v>0.31</v>
+        <v>0.315</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.205</v>
+        <v>-0.24</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.578</v>
       </c>
       <c r="F8" t="n">
-        <v>0.618</v>
+        <v>0.606</v>
       </c>
       <c r="G8" t="n">
-        <v>0.228</v>
+        <v>0.242</v>
       </c>
       <c r="H8" t="n">
         <v>0.845</v>
@@ -3986,7 +3960,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.822</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -4005,10 +3979,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.057</v>
+        <v>0.051</v>
       </c>
       <c r="C4" t="n">
-        <v>0.102</v>
+        <v>0.107</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -4026,13 +4000,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.167</v>
+        <v>0.159</v>
       </c>
       <c r="C5" t="n">
-        <v>0.294</v>
+        <v>0.276</v>
       </c>
       <c r="D5" t="n">
-        <v>0.278</v>
+        <v>0.312</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
@@ -4049,16 +4023,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.184</v>
+        <v>0.154</v>
       </c>
       <c r="C6" t="n">
-        <v>0.262</v>
+        <v>0.2</v>
       </c>
       <c r="D6" t="n">
-        <v>0.17</v>
+        <v>0.177</v>
       </c>
       <c r="E6" t="n">
-        <v>0.429</v>
+        <v>0.424</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
@@ -4074,19 +4048,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.137</v>
+        <v>0.141</v>
       </c>
       <c r="C7" t="n">
-        <v>0.145</v>
+        <v>0.156</v>
       </c>
       <c r="D7" t="n">
-        <v>0.036</v>
+        <v>0.044</v>
       </c>
       <c r="E7" t="n">
-        <v>0.121</v>
+        <v>0.126</v>
       </c>
       <c r="F7" t="n">
-        <v>0.045</v>
+        <v>0.054</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -4101,22 +4075,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.097</v>
       </c>
       <c r="C8" t="n">
-        <v>0.226</v>
+        <v>0.213</v>
       </c>
       <c r="D8" t="n">
-        <v>0.106</v>
+        <v>0.117</v>
       </c>
       <c r="E8" t="n">
-        <v>0.201</v>
+        <v>0.194</v>
       </c>
       <c r="F8" t="n">
-        <v>0.257</v>
+        <v>0.269</v>
       </c>
       <c r="G8" t="n">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -4130,25 +4104,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
       <c r="C9" t="n">
-        <v>0.036</v>
+        <v>0.021</v>
       </c>
       <c r="D9" t="n">
-        <v>0.073</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>0.146</v>
+        <v>0.158</v>
       </c>
       <c r="F9" t="n">
-        <v>0.185</v>
+        <v>0.192</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="H9" t="n">
-        <v>0.171</v>
+        <v>0.161</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
@@ -4161,28 +4135,28 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="C10" t="n">
         <v>0.122</v>
       </c>
-      <c r="C10" t="n">
-        <v>0.156</v>
-      </c>
       <c r="D10" t="n">
-        <v>0.066</v>
+        <v>0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>0.104</v>
+        <v>0.033</v>
       </c>
       <c r="F10" t="n">
-        <v>0.117</v>
+        <v>0.08</v>
       </c>
       <c r="G10" t="n">
-        <v>0.006</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
       <c r="I10" t="n">
-        <v>0.068</v>
+        <v>0.055</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -4194,31 +4168,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.321</v>
+        <v>0.324</v>
       </c>
       <c r="C11" t="n">
-        <v>0.347</v>
+        <v>0.353</v>
       </c>
       <c r="D11" t="n">
-        <v>0.229</v>
+        <v>0.267</v>
       </c>
       <c r="E11" t="n">
-        <v>0.619</v>
+        <v>0.632</v>
       </c>
       <c r="F11" t="n">
-        <v>0.705</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>0.037</v>
+        <v>0.048</v>
       </c>
       <c r="H11" t="n">
-        <v>0.251</v>
+        <v>0.266</v>
       </c>
       <c r="I11" t="n">
-        <v>0.127</v>
+        <v>0.121</v>
       </c>
       <c r="J11" t="n">
-        <v>0.042</v>
+        <v>0.029</v>
       </c>
       <c r="K11" t="inlineStr"/>
     </row>
@@ -4270,7 +4244,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.017</v>
+        <v>1.019</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -4283,10 +4257,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.017</v>
+        <v>1.019</v>
       </c>
       <c r="C3" t="n">
-        <v>1.024</v>
+        <v>1.028</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -4301,7 +4275,7 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>1.023</v>
+        <v>1.026</v>
       </c>
     </row>
     <row r="5">
@@ -4312,13 +4286,13 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1.016</v>
+        <v>1.017</v>
       </c>
       <c r="D5" t="n">
-        <v>1.073</v>
+        <v>1.093</v>
       </c>
       <c r="E5" t="n">
-        <v>1.023</v>
+        <v>1.026</v>
       </c>
     </row>
     <row r="6">
@@ -4329,7 +4303,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1.032</v>
+        <v>1.019</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -4342,7 +4316,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1.035</v>
+        <v>1.03</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -4355,7 +4329,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>1.08</v>
+        <v>1.074</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -4368,10 +4342,10 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1.093</v>
+        <v>1.084</v>
       </c>
       <c r="D9" t="n">
-        <v>1.085</v>
+        <v>1.075</v>
       </c>
       <c r="E9" t="inlineStr"/>
     </row>
@@ -4384,7 +4358,7 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>1.159</v>
+        <v>1.168</v>
       </c>
       <c r="E10" t="inlineStr"/>
     </row>
@@ -4466,25 +4440,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.74</v>
+        <v>0.753</v>
       </c>
       <c r="D2" t="n">
-        <v>0.033</v>
+        <v>0.031</v>
       </c>
       <c r="E2" t="n">
-        <v>22.326</v>
+        <v>24.501</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.67</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>1.209</v>
+        <v>1.307</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -4504,22 +4478,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.038</v>
+        <v>0.023</v>
       </c>
       <c r="D3" t="n">
-        <v>0.064</v>
+        <v>0.062</v>
       </c>
       <c r="E3" t="n">
-        <v>0.602</v>
+        <v>0.372</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5672</v>
+        <v>0.7326</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.102</v>
       </c>
       <c r="H3" t="n">
-        <v>0.162</v>
+        <v>0.143</v>
       </c>
       <c r="I3" t="n">
         <v>0.001</v>
@@ -4542,25 +4516,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.22</v>
+        <v>0.211</v>
       </c>
       <c r="D4" t="n">
-        <v>0.074</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>2.961</v>
+        <v>2.944</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0024</v>
+        <v>0.003</v>
       </c>
       <c r="G4" t="n">
-        <v>0.077</v>
+        <v>0.073</v>
       </c>
       <c r="H4" t="n">
-        <v>0.371</v>
+        <v>0.352</v>
       </c>
       <c r="I4" t="n">
-        <v>0.054</v>
+        <v>0.051</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -4580,29 +4554,29 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.136</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>1.941</v>
+        <v>1.237</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0484</v>
+        <v>0.2182</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001</v>
+        <v>-0.047</v>
       </c>
       <c r="H5" t="n">
-        <v>0.273</v>
+        <v>0.221</v>
       </c>
       <c r="I5" t="n">
-        <v>0.021</v>
+        <v>0.008</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Supported</t>
+          <t>Not supported</t>
         </is>
       </c>
     </row>
@@ -4618,25 +4592,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.226</v>
+        <v>-0.254</v>
       </c>
       <c r="D6" t="n">
         <v>0.066</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.414</v>
+        <v>-3.866</v>
       </c>
       <c r="F6" t="n">
         <v>0.0005999999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.358</v>
+        <v>-0.382</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.098</v>
+        <v>-0.125</v>
       </c>
       <c r="I6" t="n">
-        <v>0.061</v>
+        <v>0.078</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -4656,25 +4630,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.051</v>
+        <v>-0.048</v>
       </c>
       <c r="D7" t="n">
         <v>0.059</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.857</v>
+        <v>-0.8070000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3884</v>
+        <v>0.4148</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.168</v>
+        <v>-0.162</v>
       </c>
       <c r="H7" t="n">
-        <v>0.064</v>
+        <v>0.068</v>
       </c>
       <c r="I7" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -4694,25 +4668,25 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.115</v>
+        <v>-0.147</v>
       </c>
       <c r="D8" t="n">
-        <v>0.045</v>
+        <v>0.046</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.534</v>
+        <v>-3.207</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0014</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.205</v>
+        <v>-0.24</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.029</v>
+        <v>-0.059</v>
       </c>
       <c r="I8" t="n">
-        <v>0.021</v>
+        <v>0.035</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -4732,25 +4706,25 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.348</v>
+        <v>0.361</v>
       </c>
       <c r="D9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.068</v>
       </c>
       <c r="E9" t="n">
-        <v>4.951</v>
+        <v>5.283</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.209</v>
+        <v>0.228</v>
       </c>
       <c r="H9" t="n">
-        <v>0.487</v>
+        <v>0.495</v>
       </c>
       <c r="I9" t="n">
-        <v>0.128</v>
+        <v>0.135</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -4770,25 +4744,25 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.6</v>
+        <v>0.582</v>
       </c>
       <c r="D10" t="n">
         <v>0.047</v>
       </c>
       <c r="E10" t="n">
-        <v>12.805</v>
+        <v>12.277</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.505</v>
+        <v>0.488</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.672</v>
       </c>
       <c r="I10" t="n">
-        <v>0.58</v>
+        <v>0.539</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>

--- a/outputs/tables/Manuscript_Results_Tables.xlsx
+++ b/outputs/tables/Manuscript_Results_Tables.xlsx
@@ -17,11 +17,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table8" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table9" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table10" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table11" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table12" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table13" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table14" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table15" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TableA1" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TableA2" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TableA3" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TableA4" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TableA5" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1105,139 +1105,203 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Construct</t>
+          <t>Hypothesis term</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Sample</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Adjusted R2</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Q2predict</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Predictive power (PLS vs. LM benchmark)</t>
+          <t>SE (HC3)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>95% CI low (BCa)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>95% CI high (BCa)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>p (bootstrap)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>p (HC3)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>f2</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>REL</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0.5669999999999999</v>
+          <t>H7a beta_M (INT_x_PDPL)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>all N (conclusions rest on this)</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>0.5649999999999999</v>
+        <v>381</v>
       </c>
       <c r="D2" t="n">
-        <v>0.443</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+        <v>-0.08989999999999999</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0486</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.2006</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-0.0072</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.0655</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0162</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0.002</v>
+          <t>H7a beta_M (INT_x_PDPL)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>without Cook's-D-flagged cases (sensitivity)</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>-0.003</v>
+        <v>353</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.014</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>None (Q2predict &lt;= 0)</t>
-        </is>
+        <v>-0.1061</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.0322</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.1716</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.0371</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.0163</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.177</v>
+          <t>H7b beta_M (INT_x_DISC)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>all N (conclusions rest on this)</t>
+        </is>
       </c>
       <c r="C4" t="n">
-        <v>0.164</v>
+        <v>381</v>
       </c>
       <c r="D4" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
+        <v>-0.0418</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1204</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.277</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.1918</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.7296</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.0005999999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ENG</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0.167</v>
+          <t>H7b beta_M (INT_x_DISC)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>without Cook's-D-flagged cases (sensitivity)</t>
+        </is>
       </c>
       <c r="C5" t="n">
-        <v>0.16</v>
+        <v>349</v>
       </c>
       <c r="D5" t="n">
-        <v>0.073</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>PI</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.388</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.261</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+        <v>-0.0586</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.0838</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.228</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.1061</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.4948</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.4844</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.0015</v>
       </c>
     </row>
   </sheetData>
@@ -1251,290 +1315,198 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Indirect path</t>
-        </is>
-      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>beta</t>
+          <t>AIP</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>boot_mean</t>
+          <t>REL</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>boot_sd</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>95% CI low</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>95% CI high</t>
+          <t>ENG</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>PDPL</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>direct_beta</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>direct_p</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ci_excludes_0</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Mediation type</t>
+          <t>PI</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>REL-&gt;TRU-&gt;ENG</t>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>AIP</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0760077714839279</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.0780674544757365</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.0306551759222176</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.0236087058210359</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.1419704131728399</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.0855127484000439</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.2182</v>
-      </c>
-      <c r="J2" t="b">
-        <v>1</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Indirect-only mediation (full)</t>
-        </is>
-      </c>
+        <v>0.861</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>INT-&gt;TRU-&gt;ENG</t>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>REL</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.0918005937067993</v>
+        <v>0.753</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.0929295902307684</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.0296936868258892</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-0.1550931078669193</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-0.0392713359831372</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.0005999999999999999</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-0.0476699106963272</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.4148</v>
-      </c>
-      <c r="J3" t="b">
-        <v>1</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Indirect-only mediation (full)</t>
-        </is>
-      </c>
+        <v>0.893</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>REL-&gt;ENG-&gt;PI</t>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>INT</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0498108203755562</v>
+        <v>0.017</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0500978120699272</v>
+        <v>-0.074</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0407940005742073</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-0.0273094679696942</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.132291327272095</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.2182</v>
-      </c>
+        <v>0.854</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>N/A (no direct path in model)</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>INT-&gt;ENG-&gt;PI</t>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>TRU</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.0277675247660773</v>
+        <v>0.149</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.0276163230228993</v>
+        <v>0.264</v>
       </c>
       <c r="D5" t="n">
-        <v>0.034181178481901</v>
+        <v>-0.292</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.092662973381548</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.0406744150814752</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.4148</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-0.1468015323307813</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.0014</v>
-      </c>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Direct-only (no mediation)</t>
-        </is>
-      </c>
+        <v>0.837</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>REL-&gt;TRU-&gt;ENG-&gt;PI</t>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>ENG</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0442742108442197</v>
+        <v>0.135</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0457972923449941</v>
+        <v>0.184</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0190263543003398</v>
+        <v>-0.159</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0133995115424782</v>
+        <v>0.397</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0869960542872598</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.003</v>
-      </c>
+        <v>0.772</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>N/A (no direct path in model)</t>
-        </is>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>INT-&gt;TRU-&gt;ENG-&gt;PI</t>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>PDPL</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.0534734641214788</v>
+        <v>0.082</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.0544942498465238</v>
+        <v>0.192</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0187108337413342</v>
+        <v>-0.099</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0951208510862783</v>
+        <v>0.186</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0217983927585407</v>
+        <v>0.239</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0005999999999999999</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-0.1468015323307813</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.0014</v>
-      </c>
-      <c r="J7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Complementary (partial)</t>
-        </is>
+        <v>0.846</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.578</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.606</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.845</v>
       </c>
     </row>
   </sheetData>
@@ -1548,187 +1520,160 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>hypothesis</t>
+          <t>Predictor \ Outcome</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>analysis</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Breusch-Pagan LM</t>
+          <t>ENG</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BP df</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>BP p</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>White LM</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>White df</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>White p</t>
+          <t>PI</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>H7a</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>all N (conclusions rest on this)</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>381</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.0399</v>
-      </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.349</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>AIP</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.019</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>H7a</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>without Cook's-D-flagged cases (sensitivity)</t>
-        </is>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>DISC</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1.019</v>
       </c>
       <c r="C3" t="n">
-        <v>348</v>
-      </c>
-      <c r="D3" t="n">
-        <v>11.3732</v>
-      </c>
-      <c r="E3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.0445</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2.2451</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.3254</v>
-      </c>
+        <v>1.028</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>H7b</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>all N (conclusions rest on this)</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>381</v>
-      </c>
-      <c r="D4" t="n">
-        <v>19.3283</v>
-      </c>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>5</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.0017</v>
-      </c>
-      <c r="G4" t="n">
-        <v>16.0177</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.0003</v>
+        <v>1.026</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>H7b</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>without Cook's-D-flagged cases (sensitivity)</t>
-        </is>
-      </c>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>349</v>
+        <v>1.017</v>
       </c>
       <c r="D5" t="n">
-        <v>9.1982</v>
+        <v>1.093</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.1014</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.9137</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.3841</v>
-      </c>
+        <v>1.026</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>INT*DISC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>1.019</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>INT*PDPL</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>PDPL</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="n">
+        <v>1.074</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>REL</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="n">
+        <v>1.084</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.075</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>1.168</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1741,18 +1686,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hypothesis term</t>
+          <t>hypothesis</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Sample</t>
+          <t>analysis</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -1762,44 +1707,39 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>Breusch-Pagan LM</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>SE (HC3)</t>
+          <t>BP df</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>95% CI low (BCa)</t>
+          <t>BP p</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>95% CI high (BCa)</t>
+          <t>White LM</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>p (bootstrap)</t>
+          <t>White df</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>p (HC3)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>f2</t>
+          <t>White p</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>H7a beta_M (INT_x_PDPL)</t>
+          <t>H7a</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1811,31 +1751,28 @@
         <v>381</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0917</v>
+        <v>17.866</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0517</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2067</v>
+        <v>0.0005</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.0048</v>
+        <v>42.1532</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0472</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0769</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.0179</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>H7a beta_M (INT_x_PDPL)</t>
+          <t>H7a</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1844,34 +1781,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0718</v>
+        <v>9.578900000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>0.025</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1263</v>
+        <v>0.0225</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0175</v>
+        <v>1.9595</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0176</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0044</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.012</v>
+        <v>0.3754</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H7b beta_M (INT_x_DISC)</t>
+          <t>H7b</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1883,31 +1817,28 @@
         <v>381</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0024</v>
+        <v>17.2491</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1198</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2329</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2302</v>
+        <v>51.8815</v>
       </c>
       <c r="H4" t="n">
-        <v>0.978</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9844000000000001</v>
-      </c>
-      <c r="J4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H7b beta_M (INT_x_DISC)</t>
+          <t>H7b</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1919,25 +1850,22 @@
         <v>349</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0381</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.076</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1825</v>
+        <v>0.0359</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1106</v>
+        <v>7.359</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6124000000000001</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6162</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.0008</v>
+        <v>0.0252</v>
       </c>
     </row>
   </sheetData>
@@ -1951,7 +1879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1972,52 +1900,82 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>n (Pooled with REL (A-15 form))</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>estimate (Cook's D-trimmed)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>estimate (Full sample)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>estimate (Pooled with REL (A-15 form))</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>bca_low (Cook's D-trimmed)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>bca_low (Full sample)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>bca_low (Pooled with REL (A-15 form))</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>bca_high (Cook's D-trimmed)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>bca_high (Full sample)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>bca_high (Pooled with REL (A-15 form))</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>p_boot (Cook's D-trimmed)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>p_boot (Full sample)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>p_boot (Pooled with REL (A-15 form))</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ci_excludes_0 (Cook's D-trimmed)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>ci_excludes_0 (Full sample)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ci_excludes_0 (Pooled with REL (A-15 form))</t>
         </is>
       </c>
     </row>
@@ -2028,39 +1986,57 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="C2" t="n">
         <v>381</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0718</v>
+        <v>381</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.0917</v>
+        <v>-0.1061</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1263</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.2067</v>
+        <v>-0.0919</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0175</v>
+        <v>-0.1716</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0048</v>
+        <v>-0.2006</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0176</v>
+        <v>-0.2044</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0472</v>
-      </c>
-      <c r="L2" t="b">
+        <v>-0.0371</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-0.0072</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.0556</v>
+      </c>
+      <c r="Q2" t="b">
         <v>1</v>
       </c>
-      <c r="M2" t="b">
+      <c r="R2" t="b">
+        <v>1</v>
+      </c>
+      <c r="S2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2077,33 +2053,51 @@
         <v>381</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0381</v>
+        <v>381</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0024</v>
+        <v>-0.0586</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1825</v>
+        <v>-0.0418</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2329</v>
+        <v>0.0089</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1106</v>
+        <v>-0.228</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2302</v>
+        <v>-0.277</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6124000000000001</v>
+        <v>-0.2118</v>
       </c>
       <c r="K3" t="n">
-        <v>0.978</v>
-      </c>
-      <c r="L3" t="b">
+        <v>0.1061</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.1918</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.4948</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.7296</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.9772</v>
+      </c>
+      <c r="Q3" t="b">
         <v>0</v>
       </c>
-      <c r="M3" t="b">
+      <c r="R3" t="b">
+        <v>0</v>
+      </c>
+      <c r="S3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2173,16 +2167,16 @@
         <v>381</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1103</v>
+        <v>-0.1241</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2512</v>
+        <v>-0.2636</v>
       </c>
       <c r="F2" t="n">
-        <v>0.065</v>
+        <v>0.0441</v>
       </c>
       <c r="G2" t="n">
-        <v>0.18</v>
+        <v>0.1192</v>
       </c>
     </row>
     <row r="3">
@@ -2200,13 +2194,13 @@
         <v>381</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2128</v>
+        <v>-0.2246</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.3224</v>
+        <v>-0.3336</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0973</v>
+        <v>-0.1125</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -2227,13 +2221,13 @@
         <v>381</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3154</v>
+        <v>-0.325</v>
       </c>
       <c r="E4" t="n">
         <v>-0.4719</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1582</v>
+        <v>-0.1727</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -2251,19 +2245,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1195</v>
+        <v>-0.149</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2091</v>
+        <v>-0.2609</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0303</v>
+        <v>-0.0409</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0124</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="6">
@@ -2278,16 +2272,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1997</v>
+        <v>-0.2676</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2786</v>
+        <v>-0.3474</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1269</v>
+        <v>-0.1839</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -2305,16 +2299,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.28</v>
+        <v>-0.3861</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3887</v>
+        <v>-0.4918</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1831</v>
+        <v>-0.2742</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -2358,10 +2352,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>15.4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -2374,72 +2368,72 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>11.5</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nghệ An</t>
+          <t>Đồng Tháp</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>An Giang</t>
+          <t>Nghệ An</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Đồng Tháp</t>
+          <t>An Giang</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>7.7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cà Mau</t>
+          <t>Cần Thơ</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>5.8</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cần Thơ</t>
+          <t>Cà Mau</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="9">
@@ -2452,20 +2446,20 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ninh Bình</t>
+          <t>(missing free text)</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="11">
@@ -2478,46 +2472,46 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Vĩnh Long</t>
+          <t>Ninh Bình</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>(missing free text)</t>
+          <t>Bạc Liêu</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Bạc Liêu</t>
+          <t>Vĩnh Long</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="15">
@@ -2530,7 +2524,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="16">
@@ -2543,7 +2537,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="17">
@@ -2556,7 +2550,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="18">
@@ -2569,7 +2563,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="19">
@@ -2582,7 +2576,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="20">
@@ -2595,7 +2589,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="21">
@@ -2608,7 +2602,7 @@
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="22">
@@ -2621,7 +2615,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="23">
@@ -2634,7 +2628,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
     </row>
   </sheetData>
@@ -3676,7 +3670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3707,10 +3701,25 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>DISC</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>PDPL</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>INT*PDPL</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>INT*DISC</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>PI</t>
         </is>
@@ -3722,15 +3731,16 @@
           <t>AIP</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>0.861</v>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -3739,16 +3749,17 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.753</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.893</v>
-      </c>
+        <v>0.822</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -3757,18 +3768,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.017</v>
+        <v>0.051</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.074</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.854</v>
-      </c>
+        <v>0.107</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -3777,20 +3789,21 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.149</v>
+        <v>0.159</v>
       </c>
       <c r="C5" t="n">
-        <v>0.264</v>
+        <v>0.276</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.292</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.837</v>
-      </c>
+        <v>0.312</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -3799,76 +3812,178 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.135</v>
+        <v>0.154</v>
       </c>
       <c r="C6" t="n">
-        <v>0.184</v>
+        <v>0.2</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.159</v>
+        <v>0.177</v>
       </c>
       <c r="E6" t="n">
-        <v>0.397</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.772</v>
-      </c>
+        <v>0.424</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>PDPL</t>
+          <t>DISC</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.082</v>
+        <v>0.141</v>
       </c>
       <c r="C7" t="n">
-        <v>0.192</v>
+        <v>0.156</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.099</v>
+        <v>0.044</v>
       </c>
       <c r="E7" t="n">
-        <v>0.186</v>
+        <v>0.126</v>
       </c>
       <c r="F7" t="n">
-        <v>0.239</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.846</v>
-      </c>
+        <v>0.054</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
+          <t>PDPL</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.213</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>INT*PDPL</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.192</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>INT*DISC</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>PI</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>0.287</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="D8" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.578</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.606</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.242</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.845</v>
-      </c>
+      <c r="B11" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3881,320 +3996,402 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hypothesis</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>AIP</t>
+          <t>Path</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>REL</t>
+          <t>beta</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>t</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ENG</t>
+          <t>p</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>DISC</t>
+          <t>95% CI low</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>PDPL</t>
+          <t>95% CI high</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>INT*PDPL</t>
+          <t>f2</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>INT*DISC</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>PI</t>
+          <t>Decision</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>AIP</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AIP -&gt; REL</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.501</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.307</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>REL</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0.822</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AIP -&gt; INT</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.7326</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.102</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Not supported</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>REL -&gt; TRU</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2.944</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="I4" t="n">
         <v>0.051</v>
       </c>
-      <c r="C4" t="n">
-        <v>0.107</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0.159</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>REL -&gt; ENG</t>
+        </is>
       </c>
       <c r="C5" t="n">
-        <v>0.276</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>0.312</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.237</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2182</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.047</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Not supported</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>ENG</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.154</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>H6a</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>INT -&gt; TRU</t>
+        </is>
       </c>
       <c r="C6" t="n">
-        <v>0.2</v>
+        <v>-0.254</v>
       </c>
       <c r="D6" t="n">
-        <v>0.177</v>
+        <v>0.066</v>
       </c>
       <c r="E6" t="n">
-        <v>0.424</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+        <v>-3.866</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.382</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.125</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>DISC</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.141</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>H6b</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>INT -&gt; ENG</t>
+        </is>
       </c>
       <c r="C7" t="n">
-        <v>0.156</v>
+        <v>-0.048</v>
       </c>
       <c r="D7" t="n">
-        <v>0.044</v>
+        <v>0.059</v>
       </c>
       <c r="E7" t="n">
-        <v>0.126</v>
+        <v>-0.8070000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+        <v>0.4148</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.162</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Not supported</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>PDPL</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.097</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>H6c</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>INT -&gt; PI</t>
+        </is>
       </c>
       <c r="C8" t="n">
-        <v>0.213</v>
+        <v>-0.147</v>
       </c>
       <c r="D8" t="n">
-        <v>0.117</v>
+        <v>0.046</v>
       </c>
       <c r="E8" t="n">
-        <v>0.194</v>
+        <v>-3.207</v>
       </c>
       <c r="F8" t="n">
-        <v>0.269</v>
+        <v>0.0014</v>
       </c>
       <c r="G8" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+        <v>-0.24</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.059</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>INT*PDPL</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.025</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TRU -&gt; ENG</t>
+        </is>
       </c>
       <c r="C9" t="n">
-        <v>0.021</v>
+        <v>0.361</v>
       </c>
       <c r="D9" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.068</v>
       </c>
       <c r="E9" t="n">
-        <v>0.158</v>
+        <v>5.283</v>
       </c>
       <c r="F9" t="n">
-        <v>0.192</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.006</v>
+        <v>0.228</v>
       </c>
       <c r="H9" t="n">
-        <v>0.161</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+        <v>0.495</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Significant (established path)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>INT*DISC</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.114</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ENG -&gt; PI</t>
+        </is>
       </c>
       <c r="C10" t="n">
-        <v>0.122</v>
+        <v>0.582</v>
       </c>
       <c r="D10" t="n">
-        <v>0.04</v>
+        <v>0.047</v>
       </c>
       <c r="E10" t="n">
-        <v>0.033</v>
+        <v>12.277</v>
       </c>
       <c r="F10" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.488</v>
       </c>
       <c r="H10" t="n">
-        <v>0.022</v>
+        <v>0.672</v>
       </c>
       <c r="I10" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>PI</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.324</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.353</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.632</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.6909999999999999</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.266</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.121</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
+        <v>0.539</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Significant (established path)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4207,160 +4404,140 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Predictor \ Outcome</t>
+          <t>Construct</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Adjusted R2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Q2predict</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Predictive power (PLS vs. LM benchmark)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>REL</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.443</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B3" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.014</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>None (Q2predict &lt;= 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>TRU</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="B4" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.164</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>ENG</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="B5" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>PI</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>AIP</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1.019</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>DISC</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1.019</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1.028</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>ENG</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="n">
-        <v>1.026</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="n">
-        <v>1.017</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1.093</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1.026</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>INT*DISC</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>0.388</v>
+      </c>
       <c r="C6" t="n">
-        <v>1.019</v>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>INT*PDPL</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>PDPL</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="n">
-        <v>1.074</v>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>REL</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="n">
-        <v>1.084</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.075</v>
-      </c>
-      <c r="E9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="n">
-        <v>1.168</v>
-      </c>
-      <c r="E10" t="inlineStr"/>
+        <v>0.385</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4373,400 +4550,289 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hypothesis</t>
+          <t>Indirect path</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Path</t>
+          <t>beta</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>beta</t>
+          <t>boot_mean</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>boot_sd</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>95% CI low</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>95% CI high</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>p</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>95% CI low</t>
-        </is>
-      </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>95% CI high</t>
+          <t>direct_beta</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>f2</t>
+          <t>direct_p</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>ci_excludes_0</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Mediation type</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>AIP -&gt; REL</t>
-        </is>
+          <t>REL-&gt;TRU-&gt;ENG</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.0760077714839279</v>
       </c>
       <c r="C2" t="n">
-        <v>0.753</v>
+        <v>0.0780674544757365</v>
       </c>
       <c r="D2" t="n">
-        <v>0.031</v>
+        <v>0.0306551759222176</v>
       </c>
       <c r="E2" t="n">
-        <v>24.501</v>
+        <v>0.0236087058210359</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.1419704131728399</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.003</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.0855127484000439</v>
       </c>
       <c r="I2" t="n">
-        <v>1.307</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Supported</t>
+        <v>0.2182</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Indirect-only mediation (full)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>AIP -&gt; INT</t>
-        </is>
+          <t>INT-&gt;TRU-&gt;ENG</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>-0.0918005937067993</v>
       </c>
       <c r="C3" t="n">
-        <v>0.023</v>
+        <v>-0.0929295902307684</v>
       </c>
       <c r="D3" t="n">
-        <v>0.062</v>
+        <v>0.0296936868258892</v>
       </c>
       <c r="E3" t="n">
-        <v>0.372</v>
+        <v>-0.1550931078669193</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7326</v>
+        <v>-0.0392713359831372</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.102</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>0.143</v>
+        <v>-0.0476699106963272</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Not supported</t>
+        <v>0.4148</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Indirect-only mediation (full)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H4</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>REL -&gt; TRU</t>
-        </is>
+          <t>REL-&gt;ENG-&gt;PI</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.0498108203755562</v>
       </c>
       <c r="C4" t="n">
-        <v>0.211</v>
+        <v>0.0500978120699272</v>
       </c>
       <c r="D4" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.0407940005742073</v>
       </c>
       <c r="E4" t="n">
-        <v>2.944</v>
+        <v>-0.0273094679696942</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003</v>
+        <v>0.132291327272095</v>
       </c>
       <c r="G4" t="n">
-        <v>0.073</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.352</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Supported</t>
+        <v>0.2182</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>N/A (no direct path in model)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H5</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>REL -&gt; ENG</t>
-        </is>
+          <t>INT-&gt;ENG-&gt;PI</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>-0.0277675247660773</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08599999999999999</v>
+        <v>-0.0276163230228993</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.034181178481901</v>
       </c>
       <c r="E5" t="n">
-        <v>1.237</v>
+        <v>-0.092662973381548</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2182</v>
+        <v>0.0406744150814752</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.047</v>
+        <v>0.4148</v>
       </c>
       <c r="H5" t="n">
-        <v>0.221</v>
+        <v>-0.1468015323307813</v>
       </c>
       <c r="I5" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Not supported</t>
+        <v>0.0014</v>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Direct-only (no mediation)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H6a</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>INT -&gt; TRU</t>
-        </is>
+          <t>REL-&gt;TRU-&gt;ENG-&gt;PI</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.0442742108442197</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.254</v>
+        <v>0.0457972923449941</v>
       </c>
       <c r="D6" t="n">
-        <v>0.066</v>
+        <v>0.0190263543003398</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.866</v>
+        <v>0.0133995115424782</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0869960542872598</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.382</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-0.125</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Supported</t>
+        <v>0.003</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>N/A (no direct path in model)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H6b</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>INT -&gt; ENG</t>
-        </is>
+          <t>INT-&gt;TRU-&gt;ENG-&gt;PI</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>-0.0534734641214788</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.048</v>
+        <v>-0.0544942498465238</v>
       </c>
       <c r="D7" t="n">
-        <v>0.059</v>
+        <v>0.0187108337413342</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8070000000000001</v>
+        <v>-0.0951208510862783</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4148</v>
+        <v>-0.0217983927585407</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.162</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>0.068</v>
+        <v>-0.1468015323307813</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Not supported</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>H6c</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>INT -&gt; PI</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>-0.147</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-3.207</v>
-      </c>
-      <c r="F8" t="n">
         <v>0.0014</v>
       </c>
-      <c r="G8" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-0.059</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Supported</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>E1</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>TRU -&gt; ENG</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0.361</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.068</v>
-      </c>
-      <c r="E9" t="n">
-        <v>5.283</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.228</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Significant (established path)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>E2</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ENG -&gt; PI</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0.582</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="E10" t="n">
-        <v>12.277</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.488</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.672</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.539</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Significant (established path)</t>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Complementary (partial)</t>
         </is>
       </c>
     </row>
